--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_04-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_04-01-2026.xlsx
@@ -367,7 +367,7 @@
     <t>POA</t>
   </si>
   <si>
-    <t>SCRAPE ERROR</t>
+    <t>OOS</t>
   </si>
 </sst>
 </file>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_04-01-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_04-01-2026.xlsx
@@ -367,7 +367,7 @@
     <t>POA</t>
   </si>
   <si>
-    <t>OOS</t>
+    <t>LOGIN REQUIRED</t>
   </si>
 </sst>
 </file>
